--- a/clients/encore/testcases/encore-qa-tracker.xlsx
+++ b/clients/encore/testcases/encore-qa-tracker.xlsx
@@ -562,7 +562,7 @@
     <t>Test run summary</t>
   </si>
   <si>
-    <t>The full automated suite is run end to end each cycle. In the most recent full run: 370 checks — 344 passed, 5 did not pass, and 21 were intentionally skipped. The notes below explain the not-passing and skipped checks.</t>
+    <t>Most recent measured runs (7 Aug 2026): Terms and Conditions - 87 automated checks, 77 passed, 10 intentionally skipped, none failed. Service Charge Text - 83 automated checks, 81 passed, 2 intentionally skipped, none failed. Other modules were not run in this delivery cycle.</t>
   </si>
   <si>
     <t>Skipped checks: most cover the features named in the issues above and are paused until those issues are resolved. A couple need a location with very few history records, which the shared test office does not have.</t>
@@ -1003,12 +1003,12 @@
     <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
